--- a/WorkBot/refactor/data/orders/Webstaurant/Webstaurant_Triphammer_2025-10-03.xlsx
+++ b/WorkBot/refactor/data/orders/Webstaurant/Webstaurant_Triphammer_2025-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,6 +521,60 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>256.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>760RD5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Container - Alur Deli (5oz)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>97.99</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>97.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>500CT2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Parfait Insert - 2oz</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>40.49</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>40.49</t>
         </is>
       </c>
     </row>
